--- a/GameConfig/Protocol/message_types.xlsx
+++ b/GameConfig/Protocol/message_types.xlsx
@@ -1,38 +1,49 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityStudy\BigWorld\GameConfig\Protocol\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView windowHeight="17775"/>
-  </bookViews>
-  <sheets>
-    <sheet name="message_types" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>WPS 表格</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>message_types</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="142">
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>丶Z</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-05T08:19:34Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-05T08:19:46Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
+    <vt:lpwstr>16E5A9FEDA02453987ED954028CADEDC_12</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.28043</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
+    <vt:i4>0</vt:i4>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="148">
   <si>
     <t>name</t>
   </si>
@@ -43,7 +54,7 @@
     <t>note</t>
   </si>
   <si>
-    <t>Srv2Ct_RegisterReq</t>
+    <t>Srv2Srv_HelloReq</t>
   </si>
   <si>
     <t>1</t>
@@ -52,7 +63,7 @@
     <t>客户端探测到服务器注册应答流程</t>
   </si>
   <si>
-    <t>Ct2Srv_RegisterRsp</t>
+    <t>Srv2Srv_HelloRsp</t>
   </si>
   <si>
     <t>2</t>
@@ -458,11 +469,29 @@
   </si>
   <si>
     <t>服务器互联身份声明</t>
+  </si>
+  <si>
+    <t>Gw2Wd_ResumeEntityReq</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>gateway requests world resume</t>
+  </si>
+  <si>
+    <t>Wd2Gw_ResumeEntityRsp</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>world returns resume snapshot</t>
   </si>
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -1357,7 +1386,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1612,10 +1641,42 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityStudy\BigWorld\GameConfig\Protocol\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowHeight="17775"/>
+  </bookViews>
+  <sheets>
+    <sheet name="message_types" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="25.7142857142857" customWidth="1"/>
@@ -2240,13 +2301,24 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
-        <v>141</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/Protocol/message_types.xlsx
+++ b/GameConfig/Protocol/message_types.xlsx
@@ -1,48 +1,37 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>WPS 表格</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>工作表</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>message_types</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityStudy\BigWorld\GameConfig\Protocol\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowHeight="17775"/>
+  </bookViews>
+  <sheets>
+    <sheet name="message_types" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <cp:lastModifiedBy>丶Z</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-09-05T08:19:34Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-09-05T08:19:46Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
-    <vt:lpwstr>16E5A9FEDA02453987ED954028CADEDC_12</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
-    <vt:lpwstr>2052-12.1.0.28043</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
-    <vt:i4>0</vt:i4>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="148">
   <si>
     <t>name</t>
@@ -487,11 +476,155 @@
   </si>
   <si>
     <t>world returns resume snapshot</t>
+  </si>
+  <si>
+    <t>Ct2Wd_NewWorldNotify</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>world间新节点广播</t>
+  </si>
+  <si>
+    <t>Ct2Wd_WorldOfflineNotify</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>world间节点离线广播</t>
+  </si>
+  <si>
+    <t>Wd2Wd_HeartbeatReq</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>world间心跳</t>
+  </si>
+  <si>
+    <t>Wd2Wd_HeartbeatRsp</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>world间心跳应答</t>
+  </si>
+  <si>
+    <t>Wd2Ct_TransferPrepareReq</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>world向central申请传送</t>
+  </si>
+  <si>
+    <t>Ct2Wd_TransferIncomingNotify</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>central通知目标world预占</t>
+  </si>
+  <si>
+    <t>Wd2Ct_TransferIncomingAck</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>目标world预占结果</t>
+  </si>
+  <si>
+    <t>Ct2Wd_TransferPrepareRsp</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>central回复源world传送授权</t>
+  </si>
+  <si>
+    <t>Wd2Ct_TransferAbortReq</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>world上报传送中止</t>
+  </si>
+  <si>
+    <t>Wd2Ct_TransferReadyReq</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>目标world实体就绪</t>
+  </si>
+  <si>
+    <t>Ct2Wd_TransferFinishNotify</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>central下发传送提交或中止</t>
+  </si>
+  <si>
+    <t>Wd2Wd_TransferEntityReq</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>world间直连实体请求</t>
+  </si>
+  <si>
+    <t>Wd2Wd_TransferEntityRsp</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>world间直连实体应答</t>
+  </si>
+  <si>
+    <t>Ct2Gw_TransferCommitNotify</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>central通知gateway切换会话归属</t>
+  </si>
+  <si>
+    <t>Ct2Wd_SceneAssignNotify</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>central下发场景分配</t>
+  </si>
+  <si>
+    <t>Wd2Ct_SceneAssignAck</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>world回报场景分配结果</t>
   </si>
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -1386,7 +1519,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1641,42 +1774,10 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityStudy\BigWorld\GameConfig\Protocol\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView windowHeight="17775"/>
-  </bookViews>
-  <sheets>
-    <sheet name="message_types" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="25.7142857142857" customWidth="1"/>
@@ -2321,6 +2422,182 @@
         <v>147</v>
       </c>
     </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>148</v>
+      </c>
+      <c r="B59" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>154</v>
+      </c>
+      <c r="B61" t="s">
+        <v>155</v>
+      </c>
+      <c r="C61" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>157</v>
+      </c>
+      <c r="B62" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>160</v>
+      </c>
+      <c r="B63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C63" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>166</v>
+      </c>
+      <c r="B65" t="s">
+        <v>167</v>
+      </c>
+      <c r="C65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>172</v>
+      </c>
+      <c r="B67" t="s">
+        <v>173</v>
+      </c>
+      <c r="C67" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>178</v>
+      </c>
+      <c r="B69" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" t="s">
+        <v>182</v>
+      </c>
+      <c r="C70" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>184</v>
+      </c>
+      <c r="B71" t="s">
+        <v>185</v>
+      </c>
+      <c r="C71" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>187</v>
+      </c>
+      <c r="B72" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" t="s">
+        <v>191</v>
+      </c>
+      <c r="C73" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>193</v>
+      </c>
+      <c r="B74" t="s">
+        <v>194</v>
+      </c>
+      <c r="C74" t="s">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
